--- a/Data/Home/Context.Temperature.xlsx
+++ b/Data/Home/Context.Temperature.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H273"/>
+  <dimension ref="A1:I161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709227679</v>
+        <v>1711825270</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709256698</v>
+        <v>1711855300</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709260927</v>
+        <v>1711862564</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709270997</v>
+        <v>1711889799</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709274963</v>
+        <v>1711906582</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +634,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709282069</v>
+        <v>1711935521</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709288496</v>
+        <v>1711940246</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -689,10 +700,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709226672</v>
+        <v>1711953060</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709226790</v>
+        <v>1711968266</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +766,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709235439</v>
+        <v>1711975417</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709249527</v>
+        <v>1711992320</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -817,10 +832,11 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709253125</v>
+        <v>1712021960</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +865,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709262147</v>
+        <v>1712026960</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709271970</v>
+        <v>1712038881</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +931,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709277381</v>
+        <v>1712053972</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -945,10 +964,11 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709310183</v>
+        <v>1712062695</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1001,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709317051</v>
+        <v>1712078265</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1034,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709326991</v>
+        <v>1712108025</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709339730</v>
+        <v>1712112611</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709345257</v>
+        <v>1712124557</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709350635</v>
+        <v>1712137915</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709362295</v>
+        <v>1712146175</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709365688</v>
+        <v>1712164146</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709369189</v>
+        <v>1712193529</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709403334</v>
+        <v>1712198462</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1265,10 +1294,11 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709410429</v>
+        <v>1712210303</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1327,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709425230</v>
+        <v>1712224598</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1364,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709430624</v>
+        <v>1712231149</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1393,11 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709444310</v>
+        <v>1712251445</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1393,10 +1426,11 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709451322</v>
+        <v>1712280567</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1463,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709485341</v>
+        <v>1712285551</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1492,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709491065</v>
+        <v>1712297920</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1525,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709507312</v>
+        <v>1712313224</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709510712</v>
+        <v>1712320646</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1591,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709519004</v>
+        <v>1712343649</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1624,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709521455</v>
+        <v>1712372081</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1657,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709531205</v>
+        <v>1712379356</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709535872</v>
+        <v>1712405142</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1727,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709543236</v>
+        <v>1712424347</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1760,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709546376</v>
+        <v>1712453985</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1793,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709571214</v>
+        <v>1712458733</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1822,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709579132</v>
+        <v>1712471371</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1855,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709594663</v>
+        <v>1712486136</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1892,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709598653</v>
+        <v>1712493724</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1921,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709611484</v>
+        <v>1712516076</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1954,11 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709622346</v>
+        <v>1712544124</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1991,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709628604</v>
+        <v>1712551211</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2020,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709634820</v>
+        <v>1712576242</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2057,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709658162</v>
+        <v>1712596404</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709669136</v>
+        <v>1712625982</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709682120</v>
+        <v>1712630672</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709686141</v>
+        <v>1712644771</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709686482</v>
+        <v>1712658979</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709696179</v>
+        <v>1712666522</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2193,10 +2251,11 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709697045</v>
+        <v>1712683107</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2225,10 +2284,11 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709707283</v>
+        <v>1712712477</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709712840</v>
+        <v>1712717669</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2350,11 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709742794</v>
+        <v>1712730101</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2383,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709744518</v>
+        <v>1712744988</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2353,10 +2416,11 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709756438</v>
+        <v>1712753940</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709768176</v>
+        <v>1712769969</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2482,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709771318</v>
+        <v>1712798655</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2449,10 +2515,11 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709772503</v>
+        <v>1712803077</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2552,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709779445</v>
+        <v>1712815129</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2585,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709789170</v>
+        <v>1712830401</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2618,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709790232</v>
+        <v>1712838690</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2651,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709795498</v>
+        <v>1712856093</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2684,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709799117</v>
+        <v>1712884553</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2717,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709830941</v>
+        <v>1712889416</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2746,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709840016</v>
+        <v>1712902165</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2779,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709853763</v>
+        <v>1712917695</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2816,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709857131</v>
+        <v>1712924371</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2845,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2868,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709862590</v>
+        <v>1712948299</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2878,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2901,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709866044</v>
+        <v>1712976308</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +2911,11 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2934,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709870711</v>
+        <v>1712983430</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2948,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2967,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709876097</v>
+        <v>1713009311</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +2981,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3000,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709881936</v>
+        <v>1713028454</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3014,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3033,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709887208</v>
+        <v>1713057993</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3047,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3066,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709918625</v>
+        <v>1713062187</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2993,10 +3076,11 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3099,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709928148</v>
+        <v>1713074101</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3109,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3132,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709942495</v>
+        <v>1713090077</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3146,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709946214</v>
+        <v>1713099713</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3175,11 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3198,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709957153</v>
+        <v>1713119279</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3208,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3231,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709968352</v>
+        <v>1713148680</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3245,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3264,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709975908</v>
+        <v>1713155945</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3274,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3297,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710002295</v>
+        <v>1713174748</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3311,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3330,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710003334</v>
+        <v>1713181200</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3344,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3363,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710011869</v>
+        <v>1713184087</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3377,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3396,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710026942</v>
+        <v>1713202030</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3406,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3429,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710030567</v>
+        <v>1713206520</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3439,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3462,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710035480</v>
+        <v>1713232233</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3476,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3495,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710039315</v>
+        <v>1713237028</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3509,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3528,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710045372</v>
+        <v>1713265875</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3542,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3561,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710051558</v>
+        <v>1713274781</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3575,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3594,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710057760</v>
+        <v>1713288303</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3608,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3627,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710062407</v>
+        <v>1713318081</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3641,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3660,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710090750</v>
+        <v>1713322888</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3569,10 +3670,11 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3693,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710098866</v>
+        <v>1713335372</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3601,10 +3703,11 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3726,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710113424</v>
+        <v>1713349254</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3740,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3759,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710116940</v>
+        <v>1713356060</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3665,10 +3769,11 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3792,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710123353</v>
+        <v>1713379375</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3802,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3825,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710126550</v>
+        <v>1713407969</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3835,11 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3858,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710136347</v>
+        <v>1713415176</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3872,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3891,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710138554</v>
+        <v>1713439718</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3905,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3924,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710145826</v>
+        <v>1713461882</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3938,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3957,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710149114</v>
+        <v>1713490387</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +3971,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +3990,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710182405</v>
+        <v>1713494723</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4000,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4023,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710190843</v>
+        <v>1713506504</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4033,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4056,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710208387</v>
+        <v>1713521902</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4070,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4089,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710214409</v>
+        <v>1713530152</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4099,11 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4122,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710216217</v>
+        <v>1713548242</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4132,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4155,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710227515</v>
+        <v>1713578171</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4169,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4188,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710236316</v>
+        <v>1713582894</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4081,10 +4198,11 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4221,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710240341</v>
+        <v>1713595882</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4231,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4254,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710263831</v>
+        <v>1713611703</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4264,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4287,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710270558</v>
+        <v>1713620759</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4301,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4320,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710289995</v>
+        <v>1713633710</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4330,11 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4353,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710293811</v>
+        <v>1713662115</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4367,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4386,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710294070</v>
+        <v>1713666258</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4400,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4419,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710304426</v>
+        <v>1713677222</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4305,10 +4429,11 @@
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4452,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710305435</v>
+        <v>1713691720</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4466,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4485,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710314311</v>
+        <v>1713699293</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4499,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4518,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710319276</v>
+        <v>1713719848</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4532,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4551,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710322530</v>
+        <v>1713748317</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4565,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4584,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710323828</v>
+        <v>1713752660</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4594,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4617,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710331841</v>
+        <v>1713765059</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4627,11 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4650,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710348343</v>
+        <v>1713779108</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4529,10 +4660,11 @@
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4683,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710358365</v>
+        <v>1713785543</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4697,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4716,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710373349</v>
+        <v>1713806037</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4726,11 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4749,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710377211</v>
+        <v>1713835207</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4759,11 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4782,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710377424</v>
+        <v>1713839909</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4796,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4815,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710386777</v>
+        <v>1713852564</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4825,11 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4848,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710386856</v>
+        <v>1713866816</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4862,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4881,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710397827</v>
+        <v>1713874171</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4895,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4914,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710398903</v>
+        <v>1713897164</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4928,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4947,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710403483</v>
+        <v>1713926141</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +4961,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +4980,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710405215</v>
+        <v>1713933370</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +4990,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5013,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710413597</v>
+        <v>1713959761</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5027,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5046,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710437607</v>
+        <v>1713983854</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5060,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5079,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710447141</v>
+        <v>1714012979</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5093,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5112,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710462631</v>
+        <v>1714019719</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5126,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5145,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710466492</v>
+        <v>1714044649</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5155,11 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5178,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710479683</v>
+        <v>1714065240</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5041,10 +5188,11 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5211,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710486871</v>
+        <v>1714095184</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5225,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5244,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710493403</v>
+        <v>1714099796</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5254,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5277,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710498442</v>
+        <v>1714112952</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5137,10 +5287,11 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5310,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710526367</v>
+        <v>1714128437</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5320,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5343,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710534762</v>
+        <v>1714135900</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5357,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5376,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710547970</v>
+        <v>1714151608</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5386,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5409,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710553165</v>
+        <v>1714181544</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,10 +5419,11 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5442,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710554718</v>
+        <v>1714185795</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5456,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5475,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710571514</v>
+        <v>1714199564</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5485,11 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5508,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710609466</v>
+        <v>1714214818</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5518,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5541,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710622113</v>
+        <v>1714223604</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5555,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5574,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710631911</v>
+        <v>1714239035</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5584,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Warm</t>
+          <t>Context.Temperature.state: Cold</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5607,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710635362</v>
+        <v>1714269151</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5617,11 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
+          <t>Context.Temperature.state: Comfortable</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5640,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710647948</v>
+        <v>1714273892</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5654,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5673,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710656601</v>
+        <v>1714285845</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5521,10 +5683,11 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Comfortable</t>
+          <t>Context.Temperature.state: ExcessivelyHot</t>
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5706,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710662444</v>
+        <v>1714301916</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5553,10 +5716,11 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Context.Temperature.state: Cold</t>
+          <t>Context.Temperature.state: Warm</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5739,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710669253</v>
+        <v>1714311841</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,3590 +5753,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>1710695643</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>1710705194</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>1710720332</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>1710724306</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>1710735110</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>1710735482</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>1710741284</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>1710747066</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>1710753035</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr"/>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>1710758525</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>1710782486</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>1710790920</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>1710805993</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>1710809745</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>1710822771</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>1710832293</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>1710838863</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>1710844783</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H179" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>1710867847</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>1710878551</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>1710889910</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>1710894112</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>1710894324</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>1710904243</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>1710904941</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>1710916424</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>1710917840</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr"/>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>1710922578</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr"/>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>1710924365</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr"/>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>1710931401</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>1710955202</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>1710964748</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>1710978118</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>1710981949</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>1710982114</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>1710992106</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr"/>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>1710992642</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>1711003695</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>1711008860</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>1711020922</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>1711039982</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>1711050639</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>1711064423</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>1711068262</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>1711073144</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>1711077649</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>1711080965</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>1711089168</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>1711094460</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>1711127596</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyCold</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>1711128474</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>1711140067</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>1711151312</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>1711154853</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>1711165996</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>1711176046</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>1711181115</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>1711189910</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>1711214750</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1711224588</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1711240167</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>1711243667</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>1711248758</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>1711255204</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>1711260699</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>1711268359</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>1711275604</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>1711298019</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>1711300467</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr"/>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>1711309577</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H231" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>1711325085</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr"/>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H232" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>1711329053</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr"/>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H233" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>1711335072</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr"/>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H234" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>1711340129</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr"/>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>1711344007</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr"/>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>1711353137</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr"/>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>1711358684</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F238" t="inlineStr"/>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>1711362355</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F239" t="inlineStr"/>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>1711386778</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>1711392614</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>1711417156</v>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>1711421703</v>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr"/>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: ExcessivelyHot</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>1711441042</v>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr"/>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>1711450993</v>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr"/>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>1711452050</v>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr"/>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>1711454375</v>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>1711460742</v>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr"/>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>1711464388</v>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr"/>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>1711473269</v>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr"/>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>1711479231</v>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>1711504187</v>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>1711506771</v>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>1711509245</v>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr"/>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>1711513695</v>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr"/>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>1711523511</v>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr"/>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>1711531732</v>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>1711539752</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>1711541771</v>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr"/>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>1711546625</v>
-      </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>1711552325</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>1711560206</v>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr"/>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>1711566473</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>1711589659</v>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>1711592521</v>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr"/>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>1711594110</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>1711600021</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D268" t="n">
-        <v>1711608743</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Warm</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D269" t="n">
-        <v>1711616165</v>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr"/>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D270" t="n">
-        <v>1711624630</v>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D271" t="n">
-        <v>1711625951</v>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D272" t="n">
-        <v>1711632453</v>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Cold</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Temperature_Change</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D273" t="n">
-        <v>1711637269</v>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr"/>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>Context.Temperature.state: Comfortable</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
